--- a/data/trans_dic/P17G_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,33; 99,24</t>
+          <t>92,35; 99,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,37; 98,2</t>
+          <t>91,43; 97,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,96; 98,44</t>
+          <t>92,41; 98,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,15; 99,61</t>
+          <t>94,44; 99,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,65; 98,16</t>
+          <t>93,07; 98,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,92; 99,57</t>
+          <t>96,41; 99,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,82; 97,1</t>
+          <t>90,47; 97,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94,11; 98,49</t>
+          <t>94,16; 98,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,04; 98,29</t>
+          <t>94,17; 98,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,11; 98,55</t>
+          <t>95,39; 98,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,69; 97,07</t>
+          <t>92,53; 97,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,17; 98,48</t>
+          <t>95,23; 98,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,59; 95,32</t>
+          <t>86,58; 95,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,17; 96,82</t>
+          <t>89,3; 97,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,68; 93,87</t>
+          <t>86,25; 93,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,67; 92,03</t>
+          <t>80,66; 92,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,61; 95,55</t>
+          <t>89,75; 95,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,94; 97,41</t>
+          <t>92,95; 97,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,43; 97,89</t>
+          <t>93,67; 97,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,47; 93,81</t>
+          <t>87,41; 93,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,74; 94,65</t>
+          <t>90,04; 94,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92,43; 96,76</t>
+          <t>92,53; 96,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,21; 95,52</t>
+          <t>91,21; 95,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,39; 91,94</t>
+          <t>85,81; 92,02</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,31; 92,58</t>
+          <t>81,02; 92,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,66; 95,04</t>
+          <t>85,49; 94,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,18; 96,97</t>
+          <t>89,11; 97,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,17; 91,73</t>
+          <t>76,76; 91,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,33; 95,16</t>
+          <t>86,97; 95,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,46; 98,7</t>
+          <t>93,37; 98,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,0; 96,34</t>
+          <t>90,14; 96,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,54; 90,54</t>
+          <t>80,67; 90,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,57; 92,97</t>
+          <t>85,94; 92,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,72; 96,54</t>
+          <t>91,42; 96,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90,97; 96,05</t>
+          <t>91,01; 95,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,93; 89,93</t>
+          <t>81,14; 89,69</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,16; 91,17</t>
+          <t>81,98; 91,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,4; 95,74</t>
+          <t>86,51; 95,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,05; 90,15</t>
+          <t>80,32; 90,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,53; 93,57</t>
+          <t>85,59; 93,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,98; 96,17</t>
+          <t>91,46; 96,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,51; 95,9</t>
+          <t>90,2; 96,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,31; 93,81</t>
+          <t>86,73; 94,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,16; 93,61</t>
+          <t>84,11; 93,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,13; 93,74</t>
+          <t>88,91; 93,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90,45; 95,17</t>
+          <t>90,31; 95,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85,84; 91,54</t>
+          <t>85,82; 91,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,97; 93,13</t>
+          <t>85,83; 92,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,23; 92,74</t>
+          <t>87,9; 92,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>91,07; 95,09</t>
+          <t>91,05; 94,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,0; 93,06</t>
+          <t>89,31; 93,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,11; 92,11</t>
+          <t>86,85; 92,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,25; 95,2</t>
+          <t>91,97; 95,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,61; 97,07</t>
+          <t>94,5; 97,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,2; 95,22</t>
+          <t>92,14; 95,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,42; 92,64</t>
+          <t>88,34; 92,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91,25; 93,91</t>
+          <t>91,11; 93,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,64; 95,83</t>
+          <t>93,64; 95,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,45; 93,92</t>
+          <t>91,38; 93,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,47; 91,88</t>
+          <t>88,34; 91,69</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>117230; 126003</t>
+          <t>117255; 125983</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>160070; 172027</t>
+          <t>160165; 171439</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175053; 185369</t>
+          <t>174030; 185311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106491; 112667</t>
+          <t>106820; 112651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>198366; 210159</t>
+          <t>199270; 210325</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>223464; 231984</t>
+          <t>224619; 231988</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>221518; 236839</t>
+          <t>220670; 236958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>158189; 165542</t>
+          <t>158270; 165415</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>320759; 335231</t>
+          <t>321208; 334588</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>388186; 402245</t>
+          <t>389349; 402692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>400643; 419546</t>
+          <t>399941; 419420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>267613; 276913</t>
+          <t>267774; 276918</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164232; 180800</t>
+          <t>164209; 180739</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>208308; 226166</t>
+          <t>208619; 226600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225080; 246599</t>
+          <t>226576; 246164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148628; 169556</t>
+          <t>148608; 170082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>275474; 293728</t>
+          <t>275901; 294088</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>324349; 339948</t>
+          <t>324366; 340551</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>324370; 339869</t>
+          <t>325211; 339479</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>189849; 203610</t>
+          <t>189715; 203443</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446092; 470495</t>
+          <t>447555; 471450</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>538453; 563721</t>
+          <t>539080; 563217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>556275; 582589</t>
+          <t>556273; 581909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>342651; 368932</t>
+          <t>344322; 369271</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>115521; 133170</t>
+          <t>116533; 133419</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>152002; 166687</t>
+          <t>149938; 166552</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>154953; 168486</t>
+          <t>154827; 168882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103146; 122608</t>
+          <t>102607; 121800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>173921; 189522</t>
+          <t>173197; 189950</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>214528; 226570</t>
+          <t>214322; 226555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>223187; 238900</t>
+          <t>223514; 239008</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>119822; 134707</t>
+          <t>120022; 134149</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>296938; 318885</t>
+          <t>294752; 317891</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>371416; 390918</t>
+          <t>370191; 391019</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>383659; 405075</t>
+          <t>383801; 404048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>228592; 254005</t>
+          <t>229182; 253332</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>160487; 178076</t>
+          <t>160136; 179159</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161404; 176794</t>
+          <t>159760; 176412</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177523; 197467</t>
+          <t>175924; 197785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>179913; 196827</t>
+          <t>180044; 196752</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>298133; 315134</t>
+          <t>299728; 316304</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>294181; 311699</t>
+          <t>293176; 312223</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>261842; 284615</t>
+          <t>263123; 285460</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>305211; 339474</t>
+          <t>305024; 339635</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>466170; 490303</t>
+          <t>465022; 490788</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>460989; 485080</t>
+          <t>460313; 484619</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>448468; 478216</t>
+          <t>448363; 478289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>492587; 533624</t>
+          <t>491777; 531328</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>578628; 608216</t>
+          <t>576484; 607664</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>700171; 731094</t>
+          <t>700016; 730239</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>751017; 785293</t>
+          <t>753571; 786816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558659; 590780</t>
+          <t>557031; 591366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>967160; 998057</t>
+          <t>964140; 997163</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1075256; 1103167</t>
+          <t>1074049; 1103455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1053380; 1087911</t>
+          <t>1052613; 1087723</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>792725; 830583</t>
+          <t>792039; 831417</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1555133; 1600341</t>
+          <t>1552659; 1598206</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1784154; 1825881</t>
+          <t>1784283; 1825624</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1816540; 1865449</t>
+          <t>1815051; 1864231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1360526; 1413011</t>
+          <t>1358544; 1410118</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,35; 99,22</t>
+          <t>93,05; 99,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,43; 97,86</t>
+          <t>91,37; 97,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,41; 98,4</t>
+          <t>92,51; 98,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,44; 99,6</t>
+          <t>93,19; 99,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,07; 98,24</t>
+          <t>93,0; 98,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,41; 99,58</t>
+          <t>96,29; 99,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,47; 97,15</t>
+          <t>90,48; 97,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94,16; 98,41</t>
+          <t>94,11; 98,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,17; 98,1</t>
+          <t>93,96; 98,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,39; 98,66</t>
+          <t>95,2; 98,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,53; 97,04</t>
+          <t>92,7; 97,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,23; 98,48</t>
+          <t>95,41; 98,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,58; 95,29</t>
+          <t>86,51; 95,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,3; 97,0</t>
+          <t>89,01; 96,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,25; 93,7</t>
+          <t>86,01; 94,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,66; 92,32</t>
+          <t>81,05; 91,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,75; 95,66</t>
+          <t>89,77; 95,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,95; 97,59</t>
+          <t>93,03; 97,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,67; 97,78</t>
+          <t>93,59; 97,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,41; 93,73</t>
+          <t>88,17; 94,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,04; 94,84</t>
+          <t>89,81; 94,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92,53; 96,68</t>
+          <t>92,75; 96,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,21; 95,41</t>
+          <t>91,32; 95,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,81; 92,02</t>
+          <t>86,19; 92,09</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,02; 92,76</t>
+          <t>80,44; 92,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,49; 94,96</t>
+          <t>86,31; 95,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,11; 97,2</t>
+          <t>88,5; 97,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76,76; 91,12</t>
+          <t>76,69; 91,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,97; 95,38</t>
+          <t>86,38; 94,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,37; 98,7</t>
+          <t>94,0; 99,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,14; 96,38</t>
+          <t>89,54; 96,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,67; 90,16</t>
+          <t>82,33; 91,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,94; 92,68</t>
+          <t>86,25; 92,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,42; 96,56</t>
+          <t>91,91; 96,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91,01; 95,81</t>
+          <t>91,29; 95,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81,14; 89,69</t>
+          <t>82,53; 90,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,98; 91,72</t>
+          <t>82,2; 91,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,51; 95,53</t>
+          <t>86,94; 95,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,32; 90,3</t>
+          <t>80,68; 90,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,59; 93,54</t>
+          <t>85,1; 93,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,46; 96,52</t>
+          <t>91,16; 96,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,2; 96,06</t>
+          <t>90,35; 96,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,73; 94,09</t>
+          <t>86,51; 94,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,11; 93,65</t>
+          <t>81,97; 89,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,91; 93,84</t>
+          <t>88,76; 93,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90,31; 95,08</t>
+          <t>90,23; 94,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85,82; 91,55</t>
+          <t>85,89; 91,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,83; 92,73</t>
+          <t>84,71; 90,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>87,9; 92,66</t>
+          <t>87,93; 92,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>91,05; 94,98</t>
+          <t>91,06; 95,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,31; 93,25</t>
+          <t>88,97; 93,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,85; 92,21</t>
+          <t>86,55; 91,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,97; 95,12</t>
+          <t>92,06; 95,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,5; 97,09</t>
+          <t>94,59; 97,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,21</t>
+          <t>92,32; 95,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,34; 92,73</t>
+          <t>88,17; 91,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91,11; 93,78</t>
+          <t>91,35; 93,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,64; 95,81</t>
+          <t>93,64; 95,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,38; 93,86</t>
+          <t>91,39; 93,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,34; 91,69</t>
+          <t>88,18; 91,02</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110846</t>
+          <t>118311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>162778</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>273624</t>
+          <t>292577</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>117255; 125983</t>
+          <t>118144; 126003</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>160165; 171439</t>
+          <t>160073; 171349</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>174030; 185311</t>
+          <t>174216; 185290</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106820; 112651</t>
+          <t>112539; 120294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>199270; 210325</t>
+          <t>199114; 210368</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>224619; 231988</t>
+          <t>224326; 231994</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>220670; 236958</t>
+          <t>220675; 236972</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>158270; 165415</t>
+          <t>169233; 176828</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>321208; 334588</t>
+          <t>320461; 334500</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>389349; 402692</t>
+          <t>388573; 402197</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>399941; 419420</t>
+          <t>400688; 419431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>267774; 276918</t>
+          <t>286789; 296214</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160750</t>
+          <t>177393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>197530</t>
+          <t>224960</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>358281</t>
+          <t>402353</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164209; 180739</t>
+          <t>164077; 180860</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>208619; 226600</t>
+          <t>207923; 226012</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>226576; 246164</t>
+          <t>225954; 247189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148608; 170082</t>
+          <t>165571; 187015</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>275901; 294088</t>
+          <t>275976; 294549</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>324366; 340551</t>
+          <t>324640; 340957</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>325211; 339479</t>
+          <t>324946; 339899</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>189715; 203443</t>
+          <t>216488; 231023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447555; 471450</t>
+          <t>446454; 471618</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>539080; 563217</t>
+          <t>540316; 563712</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>556273; 581909</t>
+          <t>556989; 583020</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>344322; 369271</t>
+          <t>387698; 414235</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114492</t>
+          <t>125632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>128466</t>
+          <t>156871</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>242958</t>
+          <t>282502</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>116533; 133419</t>
+          <t>115705; 133296</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>149938; 166552</t>
+          <t>151391; 167180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>154827; 168882</t>
+          <t>153767; 168601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102607; 121800</t>
+          <t>112224; 134174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>173197; 189950</t>
+          <t>172028; 188868</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>214322; 226555</t>
+          <t>215775; 227410</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>223514; 239008</t>
+          <t>222040; 238678</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>120022; 134149</t>
+          <t>147988; 163770</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>294752; 317891</t>
+          <t>295843; 318959</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>370191; 391019</t>
+          <t>372170; 391740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>383801; 404048</t>
+          <t>384991; 404707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>229182; 253332</t>
+          <t>269105; 293804</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189099</t>
+          <t>196665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>320553</t>
+          <t>276740</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>509652</t>
+          <t>473406</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>160136; 179159</t>
+          <t>160554; 178362</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159760; 176412</t>
+          <t>160539; 176134</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>175924; 197785</t>
+          <t>176722; 198243</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>180044; 196752</t>
+          <t>186576; 204143</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>299728; 316304</t>
+          <t>298713; 315768</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>293176; 312223</t>
+          <t>293670; 312312</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>263123; 285460</t>
+          <t>262465; 285325</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>305024; 339635</t>
+          <t>263562; 287205</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>465022; 490788</t>
+          <t>464248; 490968</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>460313; 484619</t>
+          <t>459871; 483672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>448363; 478289</t>
+          <t>448723; 477929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>491777; 531328</t>
+          <t>458085; 487492</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>575187</t>
+          <t>618001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>809327</t>
+          <t>832836</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1384514</t>
+          <t>1450837</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>576484; 607664</t>
+          <t>576662; 607753</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>700016; 730239</t>
+          <t>700099; 731373</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>753571; 786816</t>
+          <t>750704; 786560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>557031; 591366</t>
+          <t>597741; 634600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>964140; 997163</t>
+          <t>965119; 997968</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1074049; 1103455</t>
+          <t>1075045; 1103089</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1052613; 1087723</t>
+          <t>1054730; 1088154</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>792039; 831417</t>
+          <t>817036; 848645</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1552659; 1598206</t>
+          <t>1556823; 1599828</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1784283; 1825624</t>
+          <t>1784250; 1826164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1815051; 1864231</t>
+          <t>1815344; 1864046</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1358544; 1410118</t>
+          <t>1426064; 1471984</t>
         </is>
       </c>
     </row>
